--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/VIRGINIA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/VIRGINIA_2010.xlsx
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C124">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C444">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C492">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C505">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C835">
